--- a/uav_doc/meeting/0806/RAG0806.xlsx
+++ b/uav_doc/meeting/0806/RAG0806.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsai0\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2B726B2-F9BF-47FC-AD7B-5C007628B94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DC160A-8F9E-4753-BEB7-D66AF8840A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{E0C504CA-6F4C-416E-A6F7-52CC4D778270}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="204">
   <si>
     <t>llama 3.3 70B Q8</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -250,12 +250,6 @@
     <t>Basis for Selection: The RunCam Phoenix 2 is the only camera in the reference data that explicitly mentions low-light conditions as part of its design and performance characteristics. Its small size, low weight, and ability to perform well in low light make it a strong candidate for nighttime missions. Other cameras in the reference data are more focused on high-resolution imaging or multispectral analysis and do not specifically highlight low-light performance.</t>
   </si>
   <si>
-    <t>Applicable Conditions: The mission requires nighttime operations with low-light conditions, necessitating components that can perform well in such environments.</t>
-  </si>
-  <si>
-    <t>Operating Temperature Range: -10 to 55 Celsius (meets the general temperature requirements for nighttime missions)</t>
-  </si>
-  <si>
     <t>Weight: 9.0 grams</t>
   </si>
   <si>
@@ -265,9 +259,6 @@
     <t>Advantages: High frame rate, low weight, and good performance in low light.</t>
   </si>
   <si>
-    <t>Basis for Selection: The RunCam Phoenix 2 is selected due to its specific mention of performing well in low-light conditions, which aligns with the nighttime mission requirements. Its high frame rate and low weight are additional advantages for FPV applications during nighttime missions. No other components in the reference data specifically highlight low-light performance as a key feature, making the RunCam Phoenix 2 the most suitable recommendation based on the provided information.</t>
-  </si>
-  <si>
     <t>翻譯RAG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -562,6 +553,145 @@
   </si>
   <si>
     <t>llama 3.3 70B q8 +tiade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22.76S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.5S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>適用條件：夜間任務的關鍵限制包括低光照條件，需要在此環境中具有高性能的元件。</t>
+  </si>
+  <si>
+    <t>工作溫度範圍：-10 至 55 攝氏（滿足夜間操作的一般溫度需求）</t>
+  </si>
+  <si>
+    <t>適合應用：此相機設計用于 FPV，並在低光照條件下表現良好，因此適合夜間任務。</t>
+  </si>
+  <si>
+    <t>優點：高幀率，低重量，在低光照下的良好性能。</t>
+  </si>
+  <si>
+    <t>選擇基礎：RunCam Phoenix 2 因其在低光照下的表現和高幀率而突出，這些是夜間 FPV 應用的關鍵因素。其輕量設計也有助於減少有效載荷重量。考慮到對低光模組的特定需求，此相機與任務需求非常吻合。參考資料中的其他元件，例如 MicaSense RedEdge-P 和 Sony Alpha 7R IV，更適合高光照條件或特定的應用，如多光譜成像和高解析度映射，分別使其不太適合夜間低光照任務。</t>
+  </si>
+  <si>
+    <t>Applicable Conditions: The key constraints for nighttime missions include low-light conditions, requiring components with high performance in such environments.</t>
+  </si>
+  <si>
+    <t>Operating Temperature Range: -10 to 55 Celsius (meets general temperature requirements for nighttime operations)</t>
+  </si>
+  <si>
+    <t>Basis for Selection: The RunCam Phoenix 2 stands out due to its low-light performance and high frame rate, which are crucial for nighttime FPV applications. Its lightweight design is also advantageous for reducing payload weight. Given the specific request for low-light module recommendations, this camera aligns well with the mission requirements. Other components in the reference data, such as the MicaSense RedEdge-P and Sony Alpha 7R IV, are more suited to high-light conditions or specific applications like multispectral imaging and high-resolution mapping, respectively, making them less ideal for nighttime low-light missions.</t>
+  </si>
+  <si>
+    <t>適用條件：夜間任務的關鍵限制包括低光照條件，需要具有高敏感度和在此類環境中表現良好的元件。</t>
+  </si>
+  <si>
+    <t>工作溫度範圍：-10 至 55 攝氏（滿足一般任務的溫度適應性）</t>
+  </si>
+  <si>
+    <t>適用應用：此相機設計用于 FPV，並在低光照條件下表現良好，因此適合夜間任務。</t>
+  </si>
+  <si>
+    <t>優點：低光照下的高性能，類比輸出，輕巧。</t>
+  </si>
+  <si>
+    <t>資料來源：參考資料 - cam-fpv-runcam-phoenix2。</t>
+  </si>
+  <si>
+    <t>選擇基礎：RunCam Phoenix 2 因其在低光照條件下的指定性能和輕量設計而突出，這對於減少夜間任務的有效載荷重量有益。根據對低光模組推薦的具體要求，此相機與任務需求非常吻合。參考資料中列出的其他元件更適合不同應用（多光譜成像或高解析度映射），且不直接滿足低光照需求，如 RunCam Phoenix 2般直接。</t>
+  </si>
+  <si>
+    <t>Applicable Conditions: The key constraints for nighttime missions include low-light conditions, requiring components with high sensitivity and performance in such environments.</t>
+  </si>
+  <si>
+    <t>Operating Temperature Range: -10 to 55 Celsius (meets general mission requirements for temperature adaptability)</t>
+  </si>
+  <si>
+    <t>Advantages: High performance in low light, analog output, lightweight.</t>
+  </si>
+  <si>
+    <t>Data Source: Reference Data - cam-fpv-runcam-phoenix2.</t>
+  </si>
+  <si>
+    <t>Basis for Selection: The RunCam Phoenix 2 stands out due to its specified performance in low-light conditions and its lightweight design, which is beneficial for reducing payload weight during nighttime missions. Given the specific request for low-light module recommendations, this camera aligns well with the mission requirements. Other components listed in the reference data are more suited to different applications (multispectral imaging or high-resolution mapping) and do not specifically address the low-light requirement as directly as the RunCam Phoenix 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">taide </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建議相機型號：RunCam Phoenix 2</t>
+  </si>
+  <si>
+    <t>適用條件：夜間飛行任務的關鍵限制因素，包括低光環境，需要在此類環境中具有高性能的組件。</t>
+  </si>
+  <si>
+    <t>建議相機：RunCam Phoenix 2</t>
+  </si>
+  <si>
+    <t>類型：FPV（第一人稱視角）攝影機</t>
+  </si>
+  <si>
+    <t>工作溫度範圍：-10至55攝氏度（符合一般夜間操作的溫度要求）</t>
+  </si>
+  <si>
+    <t>效能指標：解析度(1000)、幀率(60 fps)</t>
+  </si>
+  <si>
+    <t>重量：9.0克</t>
+  </si>
+  <si>
+    <t>適用應用：此相機設計用於FPV，表現良好於低光環境中，適合夜間飛行任務。</t>
+  </si>
+  <si>
+    <t>優點：高幀率、低重量、在低光環境中有良好的表現。</t>
+  </si>
+  <si>
+    <t>選擇依據：RunCam Phoenix 2因其在低光環境中的高性能和高幀率而被選出，對夜間FPV應用至關重要。其輕量設計也有利於減少酬載重量。其他如MicaSense RedEdge-P 和Sony Alpha 7R IV 等組件，則更適合高光環境或特定應用，如多光譜成像和高解析度製圖等，使它們在低光夜間飛行任務中較不合適。</t>
+  </si>
+  <si>
+    <t>11S</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1003,13 +1133,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D04EE6B-A0D8-4535-B538-D06EDBA143AC}">
-  <dimension ref="A1:Q488"/>
+  <dimension ref="A1:V488"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1020,7 +1150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1031,7 +1161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1042,7 +1172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1051,17 +1181,17 @@
       </c>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -1073,18 +1203,27 @@
         <v>12</v>
       </c>
       <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F8" t="s">
+        <v>169</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1096,19 +1235,22 @@
         <v>15</v>
       </c>
       <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -1120,28 +1262,31 @@
         <v>12</v>
       </c>
       <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F17" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -1153,29 +1298,32 @@
         <v>15</v>
       </c>
       <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F23" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -1187,8 +1335,11 @@
         <v>12</v>
       </c>
       <c r="E31" s="4"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F31" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1278,6 +1429,9 @@
         <v>15</v>
       </c>
       <c r="E43" s="4"/>
+      <c r="F43" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
@@ -1312,6 +1466,9 @@
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
+      <c r="G49" t="s">
+        <v>164</v>
+      </c>
       <c r="L49" s="2" t="s">
         <v>10</v>
       </c>
@@ -1389,6 +1546,9 @@
         <v>12</v>
       </c>
       <c r="E60" s="4"/>
+      <c r="F60" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
@@ -1407,14 +1567,17 @@
         <v>15</v>
       </c>
       <c r="E62" s="4"/>
+      <c r="F62" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A67" s="2" t="s">
         <v>10</v>
       </c>
@@ -1426,63 +1589,66 @@
         <v>12</v>
       </c>
       <c r="E67" s="4"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F67" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.4">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.4">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A83" s="2" t="s">
         <v>10</v>
       </c>
@@ -1494,137 +1660,143 @@
         <v>15</v>
       </c>
       <c r="E83" s="4"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F83" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A101" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C101" s="3"/>
       <c r="D101" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E101" s="4"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F101" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A104" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A106" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A107" t="s">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A108" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A109" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A110" t="s">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A111" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A112" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A113" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.4">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A117" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="4" t="s">
@@ -1632,225 +1804,271 @@
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G117" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A119" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.4">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A121" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A122" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.4">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A124" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.4">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A126" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.4">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A128" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.4">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A130" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.4">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A133" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A133" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A136" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A139" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A141" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A143" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B143" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C143" s="3"/>
+      <c r="D143" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E143" s="4"/>
+      <c r="F143" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A144" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A146" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A148" t="s">
         <v>69</v>
       </c>
-      <c r="C133" s="3"/>
-      <c r="D133" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E133" s="4"/>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A134" t="s">
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A149" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A136" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A138" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A139" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A140" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A141" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A142" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A143" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A144" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A145" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A147" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A149" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C149" s="3"/>
-      <c r="D149" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E149" s="4"/>
-      <c r="F149" s="4"/>
-      <c r="G149" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>99</v>
+        <v>181</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>82</v>
+        <v>182</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>101</v>
+        <v>183</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A156" t="s">
-        <v>103</v>
+        <v>184</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A158" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A159" t="s">
-        <v>106</v>
+      <c r="A159" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C159" s="3"/>
+      <c r="D159" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E159" s="4"/>
+      <c r="F159" s="4"/>
+      <c r="G159" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>109</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A163" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A164" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A165" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A166" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A167" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A168" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A169" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A170" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A171" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A172" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="191" spans="22:22" x14ac:dyDescent="0.4">
+      <c r="V191" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="193" spans="22:22" x14ac:dyDescent="0.4">
+      <c r="V193" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="195" spans="22:22" x14ac:dyDescent="0.4">
+      <c r="V195" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="196" spans="22:22" x14ac:dyDescent="0.4">
+      <c r="V196" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="197" spans="22:22" x14ac:dyDescent="0.4">
+      <c r="V197" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="198" spans="22:22" x14ac:dyDescent="0.4">
+      <c r="V198" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="199" spans="22:22" x14ac:dyDescent="0.4">
+      <c r="V199" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="200" spans="22:22" x14ac:dyDescent="0.4">
+      <c r="V200" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="201" spans="22:22" x14ac:dyDescent="0.4">
+      <c r="V201" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="202" spans="22:22" x14ac:dyDescent="0.4">
+      <c r="V202" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="204" spans="22:22" x14ac:dyDescent="0.4">
+      <c r="V204" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="269" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
@@ -1874,17 +2092,17 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A273" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A274" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.4">
@@ -1932,47 +2150,47 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A290" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A292" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A293" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A295" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A296" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A298" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A300" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.4">
@@ -1987,12 +2205,12 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A304" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.4">
@@ -2037,87 +2255,87 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A325" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A326" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A328" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A329" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A331" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A332" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A333" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A334" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A335" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A336" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A337" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A338" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A339" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A340" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A342" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A343" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A344" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.4">
@@ -2142,47 +2360,47 @@
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A349" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A350" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A351" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A353" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A355" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A357" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A359" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A360" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A361" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.4">
@@ -2192,72 +2410,72 @@
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A363" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A364" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A365" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A367" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A369" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A370" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A371" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A372" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A373" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A374" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A375" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A376" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A378" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A380" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.4">
@@ -2332,53 +2550,53 @@
         <v>6</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C400" s="3"/>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A401" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A403" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A404" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A405" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A406" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A407" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A408" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A409" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A411" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.4">
@@ -2428,12 +2646,12 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A424" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A425" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.4">
@@ -2441,85 +2659,85 @@
         <v>10</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C427" s="3"/>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A428" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A429" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A430" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A431" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A432" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A433" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A434" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A435" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A436" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A437" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A438" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A439" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A440" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A441" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A442" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.4">
@@ -2530,57 +2748,57 @@
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A444" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A446" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A448" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A449" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A450" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="451" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A451" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="452" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A452" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="453" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A453" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="454" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A454" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="455" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A455" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="457" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A457" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.4">
@@ -2591,57 +2809,57 @@
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A475" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A477" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A479" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A480" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="481" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A481" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="482" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A482" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="483" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A483" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="484" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A484" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="485" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A485" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="486" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A486" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="488" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A488" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2650,8 +2868,8 @@
     <mergeCell ref="B382:C382"/>
     <mergeCell ref="B400:C400"/>
     <mergeCell ref="B427:C427"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B159:C159"/>
     <mergeCell ref="B271:C271"/>
     <mergeCell ref="B277:C277"/>
     <mergeCell ref="B289:C289"/>
@@ -2677,5 +2895,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/uav_doc/meeting/0806/RAG0806.xlsx
+++ b/uav_doc/meeting/0806/RAG0806.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsai0\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DC160A-8F9E-4753-BEB7-D66AF8840A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212484F2-D07E-443D-9A47-A9F400657BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{E0C504CA-6F4C-416E-A6F7-52CC4D778270}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="201">
   <si>
     <t>llama 3.3 70B Q8</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -156,21 +156,12 @@
     <t xml:space="preserve">1. 推進與能源模組：長滯空、高功率密度 </t>
   </si>
   <si>
-    <t xml:space="preserve">1. 推進與能源模組：高空效率、垂直起降(VTOL)能力 </t>
-  </si>
-  <si>
     <t xml:space="preserve">2. 感測與數據鏈模組：低光度增強感測器、即時視訊傳輸 </t>
   </si>
   <si>
-    <t xml:space="preserve">2. 感測與數據鏈模組：熱源偵測、氣體洩漏感測器、即時資料傳輸 </t>
-  </si>
-  <si>
     <t xml:space="preserve">3. 結構與機身模組：海事環境耐用性、穩定載具平台 </t>
   </si>
   <si>
-    <t xml:space="preserve">3. 結構與機身模組：緊湊折疊設計、高山地形耐用性、高風阻抗 </t>
-  </si>
-  <si>
     <t xml:space="preserve">關鍵設計驅動要點：  </t>
   </si>
   <si>
@@ -180,24 +171,9 @@
     <t>llama 3.3 70B q6+taide</t>
   </si>
   <si>
-    <t>設計重點：</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t xml:space="preserve">2. 感測與數據鏈模組：夜視/紅外線、即時傳輸 </t>
   </si>
   <si>
-    <t>1. 推進與能源模組：高海拔效率、垂直起降(VTOL)能力</t>
-  </si>
-  <si>
-    <t>2. 感測與數據鏈模組：熱源偵測、氣體洩漏感測、即時資料傳輸</t>
-  </si>
-  <si>
-    <t>3. 結構與機身模組：緊湊折疊設計、山區地形通行性、防火材料</t>
-  </si>
-  <si>
     <t>輸入問題</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -692,6 +668,22 @@
   </si>
   <si>
     <t>11S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建議聚焦以下模組設計重點：</t>
+  </si>
+  <si>
+    <t>1. 推進與能源模組：高空效率、垂直起降（VTOL）能力。</t>
+  </si>
+  <si>
+    <t>2. 感測與資料鏈模組：熱源偵測、氣體洩漏檢測、即時數據傳輸。</t>
+  </si>
+  <si>
+    <t>3. 結構與機體模組：緊湊設計，適用於狹小空間；高強度重量比，適合山區地形。</t>
+  </si>
+  <si>
+    <t>9S</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1204,13 +1196,13 @@
       </c>
       <c r="E8" s="4"/>
       <c r="F8" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="I8" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
@@ -1236,7 +1228,7 @@
       </c>
       <c r="E11" s="4"/>
       <c r="F11" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -1263,7 +1255,7 @@
       </c>
       <c r="E17" s="4"/>
       <c r="F17" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
@@ -1299,7 +1291,7 @@
       </c>
       <c r="E23" s="4"/>
       <c r="F23" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
@@ -1336,7 +1328,7 @@
       </c>
       <c r="E31" s="4"/>
       <c r="F31" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
@@ -1344,22 +1336,22 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>10</v>
       </c>
@@ -1384,40 +1376,45 @@
       </c>
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="R37" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>31</v>
       </c>
       <c r="L38" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>32</v>
       </c>
-      <c r="L39" t="s">
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
+      <c r="L40" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
         <v>34</v>
       </c>
-      <c r="L40" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>36</v>
-      </c>
       <c r="L41" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="L42" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A43" s="2" t="s">
         <v>10</v>
       </c>
@@ -1430,30 +1427,30 @@
       </c>
       <c r="E43" s="4"/>
       <c r="F43" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A49" s="2" t="s">
         <v>10</v>
       </c>
@@ -1462,12 +1459,12 @@
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>10</v>
@@ -1477,69 +1474,69 @@
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="R49" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>31</v>
       </c>
       <c r="L50" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>32</v>
       </c>
-      <c r="L51" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L52" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L53" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.4">
       <c r="L54" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A57" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C57" s="3"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A60" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="4" t="s">
@@ -1547,20 +1544,20 @@
       </c>
       <c r="E60" s="4"/>
       <c r="F60" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="4" t="s">
@@ -1568,12 +1565,12 @@
       </c>
       <c r="E62" s="4"/>
       <c r="F62" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
@@ -1582,7 +1579,7 @@
         <v>10</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="4" t="s">
@@ -1590,62 +1587,62 @@
       </c>
       <c r="E67" s="4"/>
       <c r="F67" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.4">
@@ -1653,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="4" t="s">
@@ -1661,62 +1658,62 @@
       </c>
       <c r="E83" s="4"/>
       <c r="F83" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="99" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
@@ -1725,7 +1722,7 @@
         <v>10</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C101" s="3"/>
       <c r="D101" s="4" t="s">
@@ -1733,62 +1730,62 @@
       </c>
       <c r="E101" s="4"/>
       <c r="F101" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.4">
@@ -1796,7 +1793,7 @@
         <v>10</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="4" t="s">
@@ -1805,62 +1802,62 @@
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="G117" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.4">
@@ -1868,7 +1865,7 @@
         <v>10</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C143" s="3"/>
       <c r="D143" s="4" t="s">
@@ -1876,62 +1873,62 @@
       </c>
       <c r="E143" s="4"/>
       <c r="F143" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.4">
@@ -1939,136 +1936,136 @@
         <v>10</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C159" s="3"/>
       <c r="D159" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E159" s="4"/>
       <c r="F159" s="4"/>
       <c r="G159" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="191" spans="22:22" x14ac:dyDescent="0.4">
       <c r="V191" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="193" spans="22:22" x14ac:dyDescent="0.4">
       <c r="V193" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="195" spans="22:22" x14ac:dyDescent="0.4">
       <c r="V195" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="196" spans="22:22" x14ac:dyDescent="0.4">
       <c r="V196" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="197" spans="22:22" x14ac:dyDescent="0.4">
       <c r="V197" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="198" spans="22:22" x14ac:dyDescent="0.4">
       <c r="V198" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="199" spans="22:22" x14ac:dyDescent="0.4">
       <c r="V199" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="200" spans="22:22" x14ac:dyDescent="0.4">
       <c r="V200" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="201" spans="22:22" x14ac:dyDescent="0.4">
       <c r="V201" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="202" spans="22:22" x14ac:dyDescent="0.4">
       <c r="V202" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="204" spans="22:22" x14ac:dyDescent="0.4">
       <c r="V204" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="269" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
@@ -2092,17 +2089,17 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A273" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A274" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.4">
@@ -2150,47 +2147,47 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A290" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A292" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A293" s="6" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A295" s="6" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A296" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A298" s="6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A300" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.4">
@@ -2205,12 +2202,12 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A304" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.4">
@@ -2234,12 +2231,12 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A309" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A310" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="312" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.4"/>
@@ -2249,93 +2246,93 @@
         <v>6</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C324" s="3"/>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A325" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A326" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A328" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A329" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A331" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A332" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A333" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A334" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A335" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A336" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A337" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A338" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A339" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A340" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A342" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A343" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A344" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.4">
@@ -2360,122 +2357,122 @@
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A349" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A350" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A351" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A353" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A355" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A357" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A359" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A360" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A361" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A362" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A363" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A364" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A365" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A367" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A369" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A370" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A371" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A372" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A373" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A374" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A375" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A376" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A378" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A380" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.4">
@@ -2483,63 +2480,63 @@
         <v>10</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C382" s="3"/>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A383" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A385" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A387" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A388" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A389" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A390" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A391" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A392" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A393" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A394" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A396" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.4">
@@ -2550,108 +2547,108 @@
         <v>6</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C400" s="3"/>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A401" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A403" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A404" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A405" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A406" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A407" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A408" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A409" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A411" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A413" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A415" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A416" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A417" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A418" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A419" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A420" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A421" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A422" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A424" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A425" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.4">
@@ -2659,85 +2656,85 @@
         <v>10</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C427" s="3"/>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A428" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A429" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A430" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A431" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A432" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A433" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A434" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A435" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A436" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A437" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A438" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A439" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A440" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A441" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A442" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.4">
@@ -2748,57 +2745,57 @@
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A444" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A446" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A448" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A449" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A450" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="451" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A451" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="452" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A452" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="453" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A453" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="454" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A454" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="455" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A455" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="457" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A457" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.4">
@@ -2809,57 +2806,57 @@
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A475" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A477" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A479" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A480" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="481" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A481" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="482" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A482" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="483" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A483" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="484" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A484" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="485" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A485" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="486" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A486" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="488" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A488" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
